--- a/data/training.xlsx
+++ b/data/training.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{8011CD13-C671-4411-9B94-534D1305C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90306BBA-D702-4024-B19D-0808A4FC4152}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{8011CD13-C671-4411-9B94-534D1305C235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D49EA3E-F19E-4509-8F73-BE6929735990}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12180" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -116,6 +116,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=7NNDEytTm-Y</t>
+  </si>
+  <si>
+    <t>29 September 2026</t>
+  </si>
+  <si>
+    <t>Making Estimands Work - Practical Approaches with Implementation in Data Standards</t>
+  </si>
+  <si>
+    <t>https://psiweb.org/vod/item/eiwg-webinar--making-estimands-work---practical-approaches-with-implementation-in-data-standards</t>
   </si>
 </sst>
 </file>
@@ -187,10 +196,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
@@ -575,6 +580,17 @@
       </c>
       <c r="D8" s="1" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
